--- a/branches/release/2027.0.0/StructureDefinition-mii-pr-mikrobio-aviditaet.xlsx
+++ b/branches/release/2027.0.0/StructureDefinition-mii-pr-mikrobio-aviditaet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:21:52+00:00</t>
+    <t>2026-09-14T17:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
